--- a/output/Data and Chart Outputs/ember_europe_power_monthly.xlsx
+++ b/output/Data and Chart Outputs/ember_europe_power_monthly.xlsx
@@ -152,6 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Ireland power generation by type (Ember) (to May/26)</a:t>
             </a:r>
           </a:p>
